--- a/pools-example-single-pool-8-round-robin.xlsx
+++ b/pools-example-single-pool-8-round-robin.xlsx
@@ -2186,8 +2186,7 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="1" max="16383" man="true"/>
+  <rowBreaks count="1" manualBreakCount="1">
     <brk id="31" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>

--- a/pools-example-single-pool-8-round-robin.xlsx
+++ b/pools-example-single-pool-8-round-robin.xlsx
@@ -248,94 +248,94 @@
   </numFmts>
   <fonts count="13">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="250"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1137,16 +1137,16 @@
         <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
@@ -1163,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -1241,16 +1241,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
